--- a/jpcore-r4/feature/swg2-dental-eCS/CodeSystem-jp-dental-bodystructure-cs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/CodeSystem-jp-dental-bodystructure-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
   <si>
     <t>Property</t>
   </si>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>17</t>
+    <t>12</t>
   </si>
   <si>
     <t>Level</t>
@@ -190,36 +190,6 @@
   </si>
   <si>
     <t>近心根</t>
-  </si>
-  <si>
-    <t>TP-13-01</t>
-  </si>
-  <si>
-    <t>切端・咬合面ＩＯ（切端I又は咬合面Ｏ）</t>
-  </si>
-  <si>
-    <t>TP-14-01</t>
-  </si>
-  <si>
-    <t>唇側面・頬側面Ｂ（唇側面Ｌａ、頬側面Ｂ又は口腔前庭面Ｖ）</t>
-  </si>
-  <si>
-    <t>TP-15-01</t>
-  </si>
-  <si>
-    <t>口蓋側面・舌側面ＰＬ（口蓋側面Ｐ又は舌側面Ｌ（Ｌｉ））</t>
-  </si>
-  <si>
-    <t>TP-16-01</t>
-  </si>
-  <si>
-    <t>近心面Ｍ</t>
-  </si>
-  <si>
-    <t>TP-17-01</t>
-  </si>
-  <si>
-    <t>遠心面Ｄ</t>
   </si>
   <si>
     <t>TP-18-01</t>
@@ -555,7 +525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -716,66 +686,6 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="D18" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
